--- a/DataTables/DetailText/剧情/000_08时间过长.xlsx
+++ b/DataTables/DetailText/剧情/000_08时间过长.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B79AD6-5744-4AB8-AB48-AC3AF1BAE7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912D78B1-6106-4F23-A045-2CF16CA5C13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="5460" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -170,9 +157,6 @@
   </si>
   <si>
     <t>gameover</t>
-  </si>
-  <si>
-    <t>res://Assets/Background/000/000.png</t>
   </si>
   <si>
     <r>
@@ -262,6 +246,10 @@
   </si>
   <si>
     <t>遗憾的是这部耗尽一生编写的医书，最终没能保存下来…</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/000/000_00.png</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -479,7 +467,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -690,7 +678,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -708,7 +696,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
@@ -770,7 +758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="22" t="s">
         <v>30</v>
       </c>
@@ -1096,10 +1084,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1116,7 +1104,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1"/>
     </row>

--- a/DataTables/DetailText/剧情/000_08时间过长.xlsx
+++ b/DataTables/DetailText/剧情/000_08时间过长.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912D78B1-6106-4F23-A045-2CF16CA5C13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E97E974-3E6F-46EE-A439-0035B2428EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -157,6 +170,14 @@
   </si>
   <si>
     <t>gameover</t>
+  </si>
+  <si>
+    <t>遗憾的是这部耗尽一生编写的医书，最终没能保存下来…</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/000/000_00.png</t>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
@@ -180,17 +201,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>二十一年李</t>
+      <t>二十一年</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>东</t>
+      <t>李东璧</t>
     </r>
     <r>
       <rPr>
@@ -200,7 +221,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>壁病逝，</t>
+      <t>病逝，</t>
     </r>
     <r>
       <rPr>
@@ -244,20 +265,12 @@
     </r>
     <phoneticPr fontId="4"/>
   </si>
-  <si>
-    <t>遗憾的是这部耗尽一生编写的医书，最终没能保存下来…</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/000/000_00.png</t>
-    <phoneticPr fontId="4"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,6 +325,13 @@
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -467,7 +487,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -678,7 +698,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -696,7 +716,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
@@ -758,7 +778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1">
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="22" t="s">
         <v>30</v>
       </c>
@@ -1084,10 +1104,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1104,7 +1124,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" s="1"/>
     </row>
